--- a/ottertune-configure/ottertune-prior/random-100-match-kw-small-vocab-no-filters-midsimilar.xlsx
+++ b/ottertune-configure/ottertune-prior/random-100-match-kw-small-vocab-no-filters-midsimilar.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dzhdx\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6D61AF1-2416-47B8-A2B6-049FEF855BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5102D685-FEA2-407F-879A-1A8BC0C498F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21710" yWindow="-110" windowWidth="21820" windowHeight="37900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -177,13 +177,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -487,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V80"/>
+  <dimension ref="A1:V76"/>
   <sheetFormatPr defaultRowHeight="14.1" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.4">
@@ -562,8 +565,8 @@
       <c r="A2">
         <v>244</v>
       </c>
-      <c r="B2">
-        <v>56624</v>
+      <c r="B2" s="3">
+        <v>277</v>
       </c>
       <c r="C2" t="s">
         <v>26</v>
@@ -630,8 +633,8 @@
       <c r="A3">
         <v>245</v>
       </c>
-      <c r="B3">
-        <v>56902</v>
+      <c r="B3" s="3">
+        <v>555</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
@@ -698,8 +701,8 @@
       <c r="A4">
         <v>246</v>
       </c>
-      <c r="B4">
-        <v>57135</v>
+      <c r="B4" s="3">
+        <v>788</v>
       </c>
       <c r="C4" t="s">
         <v>26</v>
@@ -766,8 +769,8 @@
       <c r="A5">
         <v>249</v>
       </c>
-      <c r="B5">
-        <v>57915</v>
+      <c r="B5" s="3">
+        <v>1568</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -834,8 +837,8 @@
       <c r="A6">
         <v>250</v>
       </c>
-      <c r="B6">
-        <v>58126</v>
+      <c r="B6" s="3">
+        <v>1779</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
@@ -902,8 +905,8 @@
       <c r="A7">
         <v>251</v>
       </c>
-      <c r="B7">
-        <v>58355</v>
+      <c r="B7" s="3">
+        <v>2008</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
@@ -970,8 +973,8 @@
       <c r="A8">
         <v>253</v>
       </c>
-      <c r="B8">
-        <v>58843</v>
+      <c r="B8" s="3">
+        <v>2496</v>
       </c>
       <c r="C8" t="s">
         <v>27</v>
@@ -1038,8 +1041,8 @@
       <c r="A9">
         <v>254</v>
       </c>
-      <c r="B9">
-        <v>59107</v>
+      <c r="B9" s="3">
+        <v>2760</v>
       </c>
       <c r="C9" t="s">
         <v>25</v>
@@ -1106,8 +1109,8 @@
       <c r="A10">
         <v>255</v>
       </c>
-      <c r="B10">
-        <v>59385</v>
+      <c r="B10" s="3">
+        <v>3038</v>
       </c>
       <c r="C10" t="s">
         <v>27</v>
@@ -1174,8 +1177,8 @@
       <c r="A11">
         <v>256</v>
       </c>
-      <c r="B11">
-        <v>59615</v>
+      <c r="B11" s="3">
+        <v>3268</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
@@ -1242,8 +1245,8 @@
       <c r="A12">
         <v>257</v>
       </c>
-      <c r="B12">
-        <v>60133</v>
+      <c r="B12" s="3">
+        <v>3786</v>
       </c>
       <c r="C12" t="s">
         <v>22</v>
@@ -1310,8 +1313,8 @@
       <c r="A13">
         <v>258</v>
       </c>
-      <c r="B13">
-        <v>60360</v>
+      <c r="B13" s="3">
+        <v>4013</v>
       </c>
       <c r="C13" t="s">
         <v>23</v>
@@ -1378,8 +1381,8 @@
       <c r="A14">
         <v>259</v>
       </c>
-      <c r="B14">
-        <v>60877</v>
+      <c r="B14" s="3">
+        <v>4530</v>
       </c>
       <c r="C14" t="s">
         <v>26</v>
@@ -1446,8 +1449,8 @@
       <c r="A15">
         <v>260</v>
       </c>
-      <c r="B15">
-        <v>61084</v>
+      <c r="B15" s="3">
+        <v>4737</v>
       </c>
       <c r="C15" t="s">
         <v>22</v>
@@ -1514,8 +1517,8 @@
       <c r="A16">
         <v>262</v>
       </c>
-      <c r="B16">
-        <v>61504</v>
+      <c r="B16" s="3">
+        <v>5157</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
@@ -1582,8 +1585,8 @@
       <c r="A17">
         <v>263</v>
       </c>
-      <c r="B17">
-        <v>61712</v>
+      <c r="B17" s="3">
+        <v>5365</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
@@ -1650,8 +1653,8 @@
       <c r="A18">
         <v>264</v>
       </c>
-      <c r="B18">
-        <v>61918</v>
+      <c r="B18" s="3">
+        <v>5571</v>
       </c>
       <c r="C18" t="s">
         <v>28</v>
@@ -1718,8 +1721,8 @@
       <c r="A19">
         <v>265</v>
       </c>
-      <c r="B19">
-        <v>62157</v>
+      <c r="B19" s="3">
+        <v>5810</v>
       </c>
       <c r="C19" t="s">
         <v>23</v>
@@ -1786,8 +1789,8 @@
       <c r="A20">
         <v>266</v>
       </c>
-      <c r="B20">
-        <v>62386</v>
+      <c r="B20" s="3">
+        <v>6039</v>
       </c>
       <c r="C20" t="s">
         <v>23</v>
@@ -1854,8 +1857,8 @@
       <c r="A21">
         <v>267</v>
       </c>
-      <c r="B21">
-        <v>62650</v>
+      <c r="B21" s="3">
+        <v>6303</v>
       </c>
       <c r="C21" t="s">
         <v>25</v>
@@ -1922,8 +1925,8 @@
       <c r="A22">
         <v>268</v>
       </c>
-      <c r="B22">
-        <v>62930</v>
+      <c r="B22" s="3">
+        <v>6583</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
@@ -1990,8 +1993,8 @@
       <c r="A23">
         <v>269</v>
       </c>
-      <c r="B23">
-        <v>63131</v>
+      <c r="B23" s="3">
+        <v>6784</v>
       </c>
       <c r="C23" t="s">
         <v>25</v>
@@ -2058,8 +2061,8 @@
       <c r="A24">
         <v>270</v>
       </c>
-      <c r="B24">
-        <v>63372</v>
+      <c r="B24" s="3">
+        <v>7025</v>
       </c>
       <c r="C24" t="s">
         <v>28</v>
@@ -2126,8 +2129,8 @@
       <c r="A25">
         <v>271</v>
       </c>
-      <c r="B25">
-        <v>63590</v>
+      <c r="B25" s="3">
+        <v>7243</v>
       </c>
       <c r="C25" t="s">
         <v>28</v>
@@ -2194,8 +2197,8 @@
       <c r="A26">
         <v>272</v>
       </c>
-      <c r="B26">
-        <v>63858</v>
+      <c r="B26" s="3">
+        <v>7511</v>
       </c>
       <c r="C26" t="s">
         <v>23</v>
@@ -2262,8 +2265,8 @@
       <c r="A27">
         <v>275</v>
       </c>
-      <c r="B27">
-        <v>64551</v>
+      <c r="B27" s="3">
+        <v>8204</v>
       </c>
       <c r="C27" t="s">
         <v>23</v>
@@ -2330,8 +2333,8 @@
       <c r="A28">
         <v>276</v>
       </c>
-      <c r="B28">
-        <v>64785</v>
+      <c r="B28" s="3">
+        <v>8438</v>
       </c>
       <c r="C28" t="s">
         <v>26</v>
@@ -2398,8 +2401,8 @@
       <c r="A29">
         <v>277</v>
       </c>
-      <c r="B29">
-        <v>64997</v>
+      <c r="B29" s="3">
+        <v>8650</v>
       </c>
       <c r="C29" t="s">
         <v>22</v>
@@ -2466,8 +2469,8 @@
       <c r="A30">
         <v>278</v>
       </c>
-      <c r="B30">
-        <v>65245</v>
+      <c r="B30" s="3">
+        <v>8898</v>
       </c>
       <c r="C30" t="s">
         <v>25</v>
@@ -2534,8 +2537,8 @@
       <c r="A31">
         <v>280</v>
       </c>
-      <c r="B31">
-        <v>65757</v>
+      <c r="B31" s="3">
+        <v>9410</v>
       </c>
       <c r="C31" t="s">
         <v>27</v>
@@ -2602,8 +2605,8 @@
       <c r="A32">
         <v>283</v>
       </c>
-      <c r="B32">
-        <v>66510</v>
+      <c r="B32" s="3">
+        <v>10163</v>
       </c>
       <c r="C32" t="s">
         <v>26</v>
@@ -2670,8 +2673,8 @@
       <c r="A33">
         <v>284</v>
       </c>
-      <c r="B33">
-        <v>66740</v>
+      <c r="B33" s="3">
+        <v>10393</v>
       </c>
       <c r="C33" t="s">
         <v>26</v>
@@ -2738,8 +2741,8 @@
       <c r="A34">
         <v>285</v>
       </c>
-      <c r="B34">
-        <v>67019</v>
+      <c r="B34" s="3">
+        <v>10672</v>
       </c>
       <c r="C34" t="s">
         <v>27</v>
@@ -2806,8 +2809,8 @@
       <c r="A35">
         <v>286</v>
       </c>
-      <c r="B35">
-        <v>67250</v>
+      <c r="B35" s="3">
+        <v>10903</v>
       </c>
       <c r="C35" t="s">
         <v>26</v>
@@ -2874,8 +2877,8 @@
       <c r="A36">
         <v>287</v>
       </c>
-      <c r="B36">
-        <v>67648</v>
+      <c r="B36" s="3">
+        <v>11301</v>
       </c>
       <c r="C36" t="s">
         <v>25</v>
@@ -2942,8 +2945,8 @@
       <c r="A37">
         <v>288</v>
       </c>
-      <c r="B37">
-        <v>67858</v>
+      <c r="B37" s="3">
+        <v>11511</v>
       </c>
       <c r="C37" t="s">
         <v>22</v>
@@ -3010,8 +3013,8 @@
       <c r="A38">
         <v>291</v>
       </c>
-      <c r="B38">
-        <v>68589</v>
+      <c r="B38" s="3">
+        <v>12242</v>
       </c>
       <c r="C38" t="s">
         <v>27</v>
@@ -3078,8 +3081,8 @@
       <c r="A39">
         <v>292</v>
       </c>
-      <c r="B39">
-        <v>68809</v>
+      <c r="B39" s="3">
+        <v>12462</v>
       </c>
       <c r="C39" t="s">
         <v>24</v>
@@ -3146,8 +3149,8 @@
       <c r="A40">
         <v>293</v>
       </c>
-      <c r="B40">
-        <v>69088</v>
+      <c r="B40" s="3">
+        <v>12741</v>
       </c>
       <c r="C40" t="s">
         <v>27</v>
@@ -3214,8 +3217,8 @@
       <c r="A41">
         <v>294</v>
       </c>
-      <c r="B41">
-        <v>69297</v>
+      <c r="B41" s="3">
+        <v>12950</v>
       </c>
       <c r="C41" t="s">
         <v>22</v>
@@ -3282,8 +3285,8 @@
       <c r="A42">
         <v>296</v>
       </c>
-      <c r="B42">
-        <v>69754</v>
+      <c r="B42" s="3">
+        <v>13407</v>
       </c>
       <c r="C42" t="s">
         <v>28</v>
@@ -3350,8 +3353,8 @@
       <c r="A43">
         <v>297</v>
       </c>
-      <c r="B43">
-        <v>69961</v>
+      <c r="B43" s="3">
+        <v>13614</v>
       </c>
       <c r="C43" t="s">
         <v>22</v>
@@ -3418,8 +3421,8 @@
       <c r="A44">
         <v>298</v>
       </c>
-      <c r="B44">
-        <v>70240</v>
+      <c r="B44" s="3">
+        <v>13893</v>
       </c>
       <c r="C44" t="s">
         <v>27</v>
@@ -3486,8 +3489,8 @@
       <c r="A45">
         <v>301</v>
       </c>
-      <c r="B45">
-        <v>71212</v>
+      <c r="B45" s="3">
+        <v>14865</v>
       </c>
       <c r="C45" t="s">
         <v>26</v>
@@ -3554,8 +3557,8 @@
       <c r="A46">
         <v>302</v>
       </c>
-      <c r="B46">
-        <v>71436</v>
+      <c r="B46" s="3">
+        <v>15089</v>
       </c>
       <c r="C46" t="s">
         <v>26</v>
@@ -3622,8 +3625,8 @@
       <c r="A47">
         <v>303</v>
       </c>
-      <c r="B47">
-        <v>71665</v>
+      <c r="B47" s="3">
+        <v>15318</v>
       </c>
       <c r="C47" t="s">
         <v>26</v>
@@ -3690,8 +3693,8 @@
       <c r="A48">
         <v>305</v>
       </c>
-      <c r="B48">
-        <v>72784</v>
+      <c r="B48" s="3">
+        <v>16437</v>
       </c>
       <c r="C48" t="s">
         <v>26</v>
@@ -3758,8 +3761,8 @@
       <c r="A49">
         <v>307</v>
       </c>
-      <c r="B49">
-        <v>73247</v>
+      <c r="B49" s="3">
+        <v>16900</v>
       </c>
       <c r="C49" t="s">
         <v>26</v>
@@ -3826,8 +3829,8 @@
       <c r="A50">
         <v>308</v>
       </c>
-      <c r="B50">
-        <v>73475</v>
+      <c r="B50" s="3">
+        <v>17128</v>
       </c>
       <c r="C50" t="s">
         <v>26</v>
@@ -3894,8 +3897,8 @@
       <c r="A51">
         <v>309</v>
       </c>
-      <c r="B51">
-        <v>73697</v>
+      <c r="B51" s="3">
+        <v>17350</v>
       </c>
       <c r="C51" t="s">
         <v>26</v>
@@ -3962,8 +3965,8 @@
       <c r="A52">
         <v>310</v>
       </c>
-      <c r="B52">
-        <v>73956</v>
+      <c r="B52" s="3">
+        <v>17609</v>
       </c>
       <c r="C52" t="s">
         <v>23</v>
@@ -4030,8 +4033,8 @@
       <c r="A53">
         <v>312</v>
       </c>
-      <c r="B53">
-        <v>74398</v>
+      <c r="B53" s="3">
+        <v>18051</v>
       </c>
       <c r="C53" t="s">
         <v>26</v>
@@ -4098,8 +4101,8 @@
       <c r="A54">
         <v>314</v>
       </c>
-      <c r="B54">
-        <v>74963</v>
+      <c r="B54" s="3">
+        <v>18616</v>
       </c>
       <c r="C54" t="s">
         <v>22</v>
@@ -4166,8 +4169,8 @@
       <c r="A55">
         <v>315</v>
       </c>
-      <c r="B55">
-        <v>75196</v>
+      <c r="B55" s="3">
+        <v>18849</v>
       </c>
       <c r="C55" t="s">
         <v>26</v>
@@ -4234,8 +4237,8 @@
       <c r="A56">
         <v>316</v>
       </c>
-      <c r="B56">
-        <v>75417</v>
+      <c r="B56" s="3">
+        <v>19070</v>
       </c>
       <c r="C56" t="s">
         <v>24</v>
@@ -4302,8 +4305,8 @@
       <c r="A57">
         <v>317</v>
       </c>
-      <c r="B57">
-        <v>75696</v>
+      <c r="B57" s="3">
+        <v>19349</v>
       </c>
       <c r="C57" t="s">
         <v>27</v>
@@ -4370,8 +4373,8 @@
       <c r="A58">
         <v>318</v>
       </c>
-      <c r="B58">
-        <v>75956</v>
+      <c r="B58" s="3">
+        <v>19609</v>
       </c>
       <c r="C58" t="s">
         <v>28</v>
@@ -4438,8 +4441,8 @@
       <c r="A59">
         <v>319</v>
       </c>
-      <c r="B59">
-        <v>76235</v>
+      <c r="B59" s="3">
+        <v>19888</v>
       </c>
       <c r="C59" t="s">
         <v>27</v>
@@ -4506,8 +4509,8 @@
       <c r="A60">
         <v>323</v>
       </c>
-      <c r="B60">
-        <v>77206</v>
+      <c r="B60" s="3">
+        <v>20859</v>
       </c>
       <c r="C60" t="s">
         <v>24</v>
@@ -4574,8 +4577,8 @@
       <c r="A61">
         <v>324</v>
       </c>
-      <c r="B61">
-        <v>77436</v>
+      <c r="B61" s="3">
+        <v>21089</v>
       </c>
       <c r="C61" t="s">
         <v>26</v>
@@ -4642,8 +4645,8 @@
       <c r="A62">
         <v>325</v>
       </c>
-      <c r="B62">
-        <v>77644</v>
+      <c r="B62" s="3">
+        <v>21297</v>
       </c>
       <c r="C62" t="s">
         <v>22</v>
@@ -4710,8 +4713,8 @@
       <c r="A63">
         <v>326</v>
       </c>
-      <c r="B63">
-        <v>77853</v>
+      <c r="B63" s="3">
+        <v>21506</v>
       </c>
       <c r="C63" t="s">
         <v>22</v>
@@ -4778,8 +4781,8 @@
       <c r="A64">
         <v>327</v>
       </c>
-      <c r="B64">
-        <v>78057</v>
+      <c r="B64" s="3">
+        <v>21710</v>
       </c>
       <c r="C64" t="s">
         <v>28</v>
@@ -4846,8 +4849,8 @@
       <c r="A65">
         <v>328</v>
       </c>
-      <c r="B65">
-        <v>78290</v>
+      <c r="B65" s="3">
+        <v>21943</v>
       </c>
       <c r="C65" t="s">
         <v>26</v>
@@ -4914,8 +4917,8 @@
       <c r="A66">
         <v>329</v>
       </c>
-      <c r="B66">
-        <v>78571</v>
+      <c r="B66" s="3">
+        <v>22224</v>
       </c>
       <c r="C66" t="s">
         <v>27</v>
@@ -4982,8 +4985,8 @@
       <c r="A67">
         <v>330</v>
       </c>
-      <c r="B67">
-        <v>78802</v>
+      <c r="B67" s="3">
+        <v>22455</v>
       </c>
       <c r="C67" t="s">
         <v>24</v>
@@ -5050,8 +5053,8 @@
       <c r="A68">
         <v>331</v>
       </c>
-      <c r="B68">
-        <v>79016</v>
+      <c r="B68" s="3">
+        <v>22669</v>
       </c>
       <c r="C68" t="s">
         <v>28</v>
@@ -5118,8 +5121,8 @@
       <c r="A69">
         <v>332</v>
       </c>
-      <c r="B69">
-        <v>79248</v>
+      <c r="B69" s="3">
+        <v>22901</v>
       </c>
       <c r="C69" t="s">
         <v>26</v>
@@ -5186,8 +5189,8 @@
       <c r="A70">
         <v>333</v>
       </c>
-      <c r="B70">
-        <v>79527</v>
+      <c r="B70" s="3">
+        <v>23180</v>
       </c>
       <c r="C70" t="s">
         <v>27</v>
@@ -5254,8 +5257,8 @@
       <c r="A71">
         <v>334</v>
       </c>
-      <c r="B71">
-        <v>80089</v>
+      <c r="B71" s="3">
+        <v>23742</v>
       </c>
       <c r="C71" t="s">
         <v>28</v>
@@ -5322,8 +5325,8 @@
       <c r="A72">
         <v>335</v>
       </c>
-      <c r="B72">
-        <v>80314</v>
+      <c r="B72" s="3">
+        <v>23967</v>
       </c>
       <c r="C72" t="s">
         <v>23</v>
@@ -5390,8 +5393,8 @@
       <c r="A73">
         <v>339</v>
       </c>
-      <c r="B73">
-        <v>81243</v>
+      <c r="B73" s="3">
+        <v>24896</v>
       </c>
       <c r="C73" t="s">
         <v>27</v>
@@ -5458,8 +5461,8 @@
       <c r="A74">
         <v>340</v>
       </c>
-      <c r="B74">
-        <v>81522</v>
+      <c r="B74" s="3">
+        <v>25175</v>
       </c>
       <c r="C74" t="s">
         <v>27</v>
@@ -5526,8 +5529,8 @@
       <c r="A75">
         <v>342</v>
       </c>
-      <c r="B75">
-        <v>82168</v>
+      <c r="B75" s="3">
+        <v>25821</v>
       </c>
       <c r="C75" t="s">
         <v>25</v>
@@ -5594,8 +5597,8 @@
       <c r="A76">
         <v>343</v>
       </c>
-      <c r="B76">
-        <v>82448</v>
+      <c r="B76" s="3">
+        <v>26101</v>
       </c>
       <c r="C76" t="s">
         <v>27</v>
@@ -5656,38 +5659,6 @@
       </c>
       <c r="V76">
         <v>109.4134770223305</v>
-      </c>
-    </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="T77">
-        <v>6.7037267645355295E-2</v>
-      </c>
-      <c r="U77">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="T78">
-        <v>4.3645288224797692E-2</v>
-      </c>
-      <c r="U78">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="T79">
-        <v>5.7313507911749162E-2</v>
-      </c>
-      <c r="U79">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.4">
-      <c r="T80">
-        <v>1.9809874671045679E-2</v>
-      </c>
-      <c r="U80">
-        <v>230</v>
       </c>
     </row>
   </sheetData>
